--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4464,7 +4464,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 16.0, "op_wape_pct": 180.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 83.53, "rev_act": 97.77, "op_pred": 2.39, "op_act": -3.27}, {"q": "2025Q4", "rev_pred": 115.84, "rev_act": 89.99, "op_pred": 3.32, "op_act": -2.78}, {"q": "2026Q1", "rev_pred": 79.11, "rev_act": 88.26, "op_pred": 2.27, "op_act": 0.59}, {"q": "2026Q2", "rev_pred": 97.99, "rev_act": 110.76, "op_pred": 2.81, "op_act": 1.53}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 16.0, "op_wape_pct": 180.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 83.53, "rev_act": 97.77, "op_pred": 2.39, "op_act": -3.27}, {"q": "2025Q4", "rev_pred": 115.84, "rev_act": 89.99, "op_pred": 3.32, "op_act": -2.78}, {"q": "2026Q1", "rev_pred": 79.11, "rev_act": 88.26, "op_pred": 2.27, "op_act": 0.59}, {"q": "2026Q2", "rev_pred": 97.99, "rev_act": 110.76, "op_pred": 2.81, "op_act": 1.53}]}</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>2680</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2730</v>
+        <v>2650</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6144,7 +6144,7 @@
         <v>2130</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2615</v>
+        <v>2605</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>2432.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2692.5</v>
+        <v>2678.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2730</v>
+        <v>2650</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>1.523521915481402e-13</v>
+        <v>3.047043830962804e-13</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03577343491222263</v>
+        <v>0.03577343491223215</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1436.84</v>
+        <v>1394.74</v>
       </c>
     </row>
     <row r="32">
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>2680</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2650</v>
+        <v>2620</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>2432.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2678.3</v>
+        <v>2666.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8962,11 +8962,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2650</v>
+        <v>2620</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,670원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,625원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1394.74</v>
+        <v>1378.95</v>
       </c>
     </row>
     <row r="32">
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>2680</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2620</v>
+        <v>2630</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6144,7 +6144,7 @@
         <v>2130</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2605</v>
+        <v>2515</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>2432.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2666.2</v>
+        <v>2659</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8962,11 +8962,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2620</v>
+        <v>2630</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,625원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,650원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1378.95</v>
+        <v>1384.21</v>
       </c>
     </row>
     <row r="32">
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>3.047043830962804e-13</v>
+        <v>1.523521915481402e-13</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03577343491223215</v>
+        <v>0.03577343491222263</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,650원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,620원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9354,7 +9354,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>1.523521915481402e-13</v>
+        <v>3.047043830962804e-13</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03577343491222263</v>
+        <v>0.03577343491223215</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
         <v>2680</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2630</v>
+        <v>2560</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>2432.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2659</v>
+        <v>2642.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2630</v>
+        <v>2560</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1384.21</v>
+        <v>1347.37</v>
       </c>
     </row>
     <row r="32">
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>2680</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2560</v>
+        <v>2535</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6144,7 +6144,7 @@
         <v>2130</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2515</v>
+        <v>2505</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>2432.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2642.5</v>
+        <v>2625.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8962,11 +8962,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2560</v>
+        <v>2535</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,620원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,630원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1347.37</v>
+        <v>1334.21</v>
       </c>
     </row>
     <row r="32">
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>2680</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2535</v>
+        <v>2500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6144,7 +6144,7 @@
         <v>2130</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2505</v>
+        <v>2450</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>2432.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2625.7</v>
+        <v>2609.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8962,11 +8962,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2535</v>
+        <v>2500</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,630원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,560원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1334.21</v>
+        <v>1315.79</v>
       </c>
     </row>
     <row r="32">
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>2680</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2500</v>
+        <v>2560</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6053,7 +6053,7 @@
         <v>2790</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>2780</v>
+        <v>2900</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>2432.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2609.4</v>
+        <v>2583.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8962,11 +8962,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2500</v>
+        <v>2560</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,560원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,480원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1315.79</v>
+        <v>1347.37</v>
       </c>
     </row>
     <row r="32">
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/025890_model.xlsx
+++ b/argus/kship/models/025890_model.xlsx
@@ -4123,7 +4123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4994,35 +4994,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5113,35 +5113,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5232,35 +5232,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5351,35 +5351,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5470,35 +5470,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5589,35 +5589,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5708,35 +5708,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5827,35 +5827,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>2680</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2560</v>
+        <v>2475</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>2432.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2583.6</v>
+        <v>2561.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8962,11 +8962,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2560</v>
+        <v>2475</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,480원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,615원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1347.37</v>
+        <v>1302.63</v>
       </c>
     </row>
     <row r="32">
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="33">
